--- a/storage/mega.xlsx
+++ b/storage/mega.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="BASE" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">BASE!$A$1:$J$160</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">BASE!$A$1:$J$162</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="251">
   <si>
     <t>id</t>
   </si>
@@ -5013,7 +5013,9 @@
       <c r="G152" s="3">
         <v>5.0</v>
       </c>
-      <c r="H152" s="4"/>
+      <c r="H152" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="I152" s="4"/>
       <c r="J152" s="4"/>
     </row>
@@ -5039,16 +5041,18 @@
       <c r="G153" s="3">
         <v>5.0</v>
       </c>
-      <c r="H153" s="4"/>
+      <c r="H153" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="I153" s="4"/>
       <c r="J153" s="4"/>
     </row>
     <row r="154">
       <c r="A154" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>11</v>
@@ -5060,23 +5064,23 @@
         <v>11</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G154" s="3">
         <v>5.0</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>242</v>
+        <v>120</v>
       </c>
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
     </row>
     <row r="155">
       <c r="A155" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>243</v>
+        <v>44</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>11</v>
@@ -5088,23 +5092,23 @@
         <v>11</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G155" s="3">
         <v>5.0</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>242</v>
+        <v>120</v>
       </c>
       <c r="I155" s="4"/>
       <c r="J155" s="4"/>
     </row>
     <row r="156">
       <c r="A156" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>11</v>
@@ -5129,10 +5133,10 @@
     </row>
     <row r="157">
       <c r="A157" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>11</v>
@@ -5144,21 +5148,23 @@
         <v>11</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G157" s="3">
         <v>5.0</v>
       </c>
-      <c r="H157" s="4"/>
+      <c r="H157" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="I157" s="4"/>
       <c r="J157" s="4"/>
     </row>
     <row r="158">
       <c r="A158" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>11</v>
@@ -5170,12 +5176,14 @@
         <v>11</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G158" s="3">
         <v>5.0</v>
       </c>
-      <c r="H158" s="4"/>
+      <c r="H158" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
     </row>
@@ -5184,7 +5192,7 @@
         <v>1.0</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>11</v>
@@ -5196,7 +5204,7 @@
         <v>11</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G159" s="3">
         <v>5.0</v>
@@ -5210,7 +5218,7 @@
         <v>2.0</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>11</v>
@@ -5222,7 +5230,7 @@
         <v>11</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G160" s="3">
         <v>5.0</v>
@@ -5231,12 +5239,64 @@
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
     </row>
+    <row r="161">
+      <c r="A161" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G161" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H161" s="4"/>
+      <c r="I161" s="4"/>
+      <c r="J161" s="4"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G162" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H162" s="4"/>
+      <c r="I162" s="4"/>
+      <c r="J162" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$J$160">
-    <sortState ref="A1:J160">
-      <sortCondition ref="F1:F160"/>
-      <sortCondition ref="E1:E160"/>
-      <sortCondition ref="C1:C160"/>
+  <autoFilter ref="$A$1:$J$162">
+    <sortState ref="A1:J162">
+      <sortCondition ref="F1:F162"/>
+      <sortCondition ref="E1:E162"/>
+      <sortCondition ref="C1:C162"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>
